--- a/database/SCCP_Master_Database_v0.1.xlsx
+++ b/database/SCCP_Master_Database_v0.1.xlsx
@@ -7,7 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="00_PROJET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_COMMANDES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_CATEGORIES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_PERIPHERIQUES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_TRADUCTIONS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_PROFILS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_STREAMDECK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_ICONES" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_TESTS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_CHANGELOG" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,4 +427,121 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/database/SCCP_Master_Database_v0.1.xlsx
+++ b/database/SCCP_Master_Database_v0.1.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,9 +460,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sous-module</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nom officiel EN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Nom SCCP FR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom XML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Raccourci clavier</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Périphérique</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fréquence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Niveau</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Version SC</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Dernière vérification</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Testeur</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Profil</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Page Stream Deck</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Icône</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Commentaires</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/database/SCCP_Master_Database_v0.1.xlsx
+++ b/database/SCCP_Master_Database_v0.1.xlsx
@@ -462,6 +462,30 @@
   </sheetPr>
   <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
